--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6799-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6799-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC629710-8FE8-4836-853C-D22D97D74B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC59BA17-99D5-4C96-8E66-4695440088B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{9048857D-B0AA-4DB8-B28C-BEE84A4D0E68}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{56525080-993F-42A2-A2BB-1A43FE8A1693}"/>
   </bookViews>
   <sheets>
     <sheet name="6799-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1534,24 +1534,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D9B965-4C34-41E9-BAB0-5B71A2C66C58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535245BA-4272-49D8-BDB8-FA149B86DEC0}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1579,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1705,7 +1705,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1759,7 +1759,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1785,7 +1785,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>2025</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2024</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
         <v>2023</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>26</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>26</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>26</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>26</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51">
         <v>2022</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="49">
         <v>2021</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="51" t="s">
         <v>49</v>
       </c>
